--- a/grc_wisdom_api/scripts/verify/_tmp_reports/RCM.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/RCM.xlsx
@@ -17,7 +17,7 @@
     <t>Risk &amp; Control Matrix</t>
   </si>
   <si>
-    <t>AUD-2026-09 — Payments incident investigation</t>
+    <t>AUD-2026-03 — Business Continuity Readiness</t>
   </si>
   <si>
     <t>Organisation</t>
@@ -44,7 +44,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-16 17:58 UTC</t>
+    <t>2026-08-17 15:43 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
